--- a/inputs/CEREBRO_Input_Lecanemab.xlsx
+++ b/inputs/CEREBRO_Input_Lecanemab.xlsx
@@ -894,8 +894,14 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>&gt;Lecanemab_VH
-QVQLVQSGAEVKKPGSSVKVSCKASGYTFTNYGMNWVRQAPGQGLEWMGWINTYTGEPTYTDDFKGRVTITTDTSTSTAYMELSSLRSEDTAVYYCARGGYDGRGFDYWGQGTLVTVSS</t>
+          <t>&gt;Lecanemab_Heavy_Chain_1
+EVQLVESGGGLVQPGGSLRLSCSASGFTFSSFGMHWVRQAPGKGLEWVAYISSGSSTIYYGDTVKGRFTISRDNAKNSLFLQMSSLRAEDTAVYYCAREGGYYYGRSYYTMDYWGQGTTVTVSSASTKGPSVFPLAPSSKSTSGGTAALGCLVKDYFPEPVTVSWNSGALTSGVHTFPAVLQSSGLYSLSSVVTVPSSSLGTQTYICNVNHKPSNTKVDKKVEPKSCDKTHTCPPCPAPELLGGPSVFLFPPKPKDTLMISRTPEVTCVVVDVSHEDPEVKFNWYVDGVEVHNAKTKPREEQYNSTYRVVSVLTVLHQDWLNGKEYKCKVSNKALPAPIEKTISKAKGQPREPQVYTLPPSRDELTKNQVSLTCLVKGFYPSDIAVEWESNGQPENNYKTTPPVLDSDGSFFLYSKLTVDKSRWQQGNVFSCSVMHEALHNHYTQKSLSLSPGK
+&gt;Lecanemab_Heavy_Chain_2
+EVQLVESGGGLVQPGGSLRLSCSASGFTFSSFGMHWVRQAPGKGLEWVAYISSGSSTIYYGDTVKGRFTISRDNAKNSLFLQMSSLRAEDTAVYYCAREGGYYYGRSYYTMDYWGQGTTVTVSSASTKGPSVFPLAPSSKSTSGGTAALGCLVKDYFPEPVTVSWNSGALTSGVHTFPAVLQSSGLYSLSSVVTVPSSSLGTQTYICNVNHKPSNTKVDKKVEPKSCDKTHTCPPCPAPELLGGPSVFLFPPKPKDTLMISRTPEVTCVVVDVSHEDPEVKFNWYVDGVEVHNAKTKPREEQYNSTYRVVSVLTVLHQDWLNGKEYKCKVSNKALPAPIEKTISKAKGQPREPQVYTLPPSRDELTKNQVSLTCLVKGFYPSDIAVEWESNGQPENNYKTTPPVLDSDGSFFLYSKLTVDKSRWQQGNVFSCSVMHEALHNHYTQKSLSLSPGK
+&gt;Lecanemab_Light_Chain_1
+DVVMTQSPLSLPVTPGAPASISCRSSQSIVHSNGNTYLEWYLQKPGQSPKLLIYKVSNRFSGVPDRFSGSGSGTDFTLRISRVEAEDVGIYYCFQGSHVPPTFGPGTKLEIKRTVAAPSVFIFPPSDEQLKSGTASVVCLLNNFYPREAKVQWKVDNALQSGNSQESVTEQDSKDSTYSLSSTLTLSKADYEKHKVYACEVTHQGLSSPVTKSFNRGEC
+&gt;Lecanemab_Light_Chain_2
+DVVMTQSPLSLPVTPGAPASISCRSSQSIVHSNGNTYLEWYLQKPGQSPKLLIYKVSNRFSGVPDRFSGSGSGTDFTLRISRVEAEDVGIYYCFQGSHVPPTFGPGTKLEIKRTVAAPSVFIFPPSDEQLKSGTASVVCLLNNFYPREAKVQWKVDNALQSGNSQESVTEQDSKDSTYSLSSTLTLSKADYEKHKVYACEVTHQGLSSPVTKSFNRGEC</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -1082,8 +1088,10 @@
           <t>MW (Da)</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
-        <v>143000</v>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>(fetched automatically)</t>
+        </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
@@ -1286,7 +1294,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
